--- a/results/intensive_linear_95p_weighted_strong/estimates/log_intensive_linear_95p_weighted_strong_both_1000perm_estimates.xlsx
+++ b/results/intensive_linear_95p_weighted_strong/estimates/log_intensive_linear_95p_weighted_strong_both_1000perm_estimates.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -389,14 +389,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ver</t>
+          <t>total_reactions</t>
         </is>
       </c>
       <c r="B2">
-        <v>0.0009504025834431058</v>
+        <v>-0.1568887780807397</v>
       </c>
       <c r="C2">
-        <v>0.05350630392306115</v>
+        <v>0.133789548230604</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -405,7 +405,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>log Verifiable Posts + Shares</t>
+          <t>log(Total reactions)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -417,14 +417,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>non_ver</t>
+          <t>total_comments</t>
         </is>
       </c>
       <c r="B3">
-        <v>-0.008383916383467731</v>
+        <v>-0.008948204082309199</v>
       </c>
       <c r="C3">
-        <v>0.08159805048222712</v>
+        <v>0.06303725908661464</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -433,7 +433,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>log Non Verifiable Posts + Shares</t>
+          <t>log(Total comments)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -445,14 +445,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>total_shares</t>
         </is>
       </c>
       <c r="B4">
-        <v>0.01365368826647307</v>
+        <v>-0.2011706281118975</v>
       </c>
       <c r="C4">
-        <v>0.02888019102888296</v>
+        <v>0.1399659354181562</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -461,7 +461,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>log True Posts + Shares</t>
+          <t>log(Total shares)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -473,14 +473,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>fake</t>
+          <t>n_posts</t>
         </is>
       </c>
       <c r="B5">
-        <v>-0.005317172673536687</v>
+        <v>-0.03616194842780929</v>
       </c>
       <c r="C5">
-        <v>0.05107193577984404</v>
+        <v>0.09634967614395903</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -489,7 +489,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>log Fake Posts + Shares</t>
+          <t>log(Number of posts + shares)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -501,14 +501,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>n_posts</t>
+          <t>eng</t>
         </is>
       </c>
       <c r="B6">
-        <v>-0.02536835242011414</v>
+        <v>-0.02146788939124671</v>
       </c>
       <c r="C6">
-        <v>0.08516360950735986</v>
+        <v>0.09542058580817139</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -517,7 +517,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>log Number of Posts + Shares</t>
+          <t>log(Number of posts + shares, English)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -529,28 +529,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ver</t>
+          <t>verifiability</t>
         </is>
       </c>
       <c r="B7">
-        <v>-0.03503700568164337</v>
+        <v>-0.009883974184068479</v>
       </c>
       <c r="C7">
-        <v>0.04301933890712132</v>
+        <v>0.06035831933855403</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>stage3_4</t>
+          <t>stage1_2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>log Verifiable Posts + Shares</t>
+          <t>log(Verifiable posts + shares)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Weeks 5-8</t>
+          <t>Weeks 1-4</t>
         </is>
       </c>
     </row>
@@ -561,24 +561,24 @@
         </is>
       </c>
       <c r="B8">
-        <v>-0.06933259342109058</v>
+        <v>-0.01880583173714792</v>
       </c>
       <c r="C8">
-        <v>0.06594653974510743</v>
+        <v>0.09242477266153648</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>stage3_4</t>
+          <t>stage1_2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>log Non Verifiable Posts + Shares</t>
+          <t>log(Non-verifiable posts + shares)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Weeks 5-8</t>
+          <t>Weeks 1-4</t>
         </is>
       </c>
     </row>
@@ -589,24 +589,24 @@
         </is>
       </c>
       <c r="B9">
-        <v>-0.01271882336141471</v>
+        <v>0.01060641833063787</v>
       </c>
       <c r="C9">
-        <v>0.0262595028667762</v>
+        <v>0.03209741223211979</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>stage3_4</t>
+          <t>stage1_2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>log True Posts + Shares</t>
+          <t>log(True posts + shares)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Weeks 5-8</t>
+          <t>Weeks 1-4</t>
         </is>
       </c>
     </row>
@@ -617,190 +617,1198 @@
         </is>
       </c>
       <c r="B10">
-        <v>-0.02853517026616686</v>
+        <v>-0.01490850381422974</v>
       </c>
       <c r="C10">
-        <v>0.03966057092586734</v>
+        <v>0.05737239122321196</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>stage3_4</t>
+          <t>stage1_2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>log Fake Posts + Shares</t>
+          <t>log(Fake posts + shares)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Weeks 5-8</t>
+          <t>Weeks 1-4</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>n_posts</t>
+          <t>n_posts_covid</t>
         </is>
       </c>
       <c r="B11">
-        <v>-0.07390889629828248</v>
+        <v>-0.004472918662178686</v>
       </c>
       <c r="C11">
-        <v>0.07203062187991138</v>
+        <v>0.009548852700429641</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>stage3_4</t>
+          <t>stage1_2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>log Number of Posts + Shares</t>
+          <t>log(COVID posts + shares)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Weeks 5-8</t>
+          <t>Weeks 1-4</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ver</t>
+          <t>pos_b_covid</t>
         </is>
       </c>
       <c r="B12">
-        <v>-0.03746338772157422</v>
+        <v>0.001720879526337047</v>
       </c>
       <c r="C12">
-        <v>0.03441023838782038</v>
+        <v>0.004639584060425705</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>stage5_6</t>
+          <t>stage1_2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>log Verifiable Posts + Shares</t>
+          <t>log(Positive COVID posts + shares)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Weeks 9-12</t>
+          <t>Weeks 1-4</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>non_ver</t>
+          <t>neutral_b_covid</t>
         </is>
       </c>
       <c r="B13">
-        <v>-0.1061050667513092</v>
+        <v>-0.004840556009014424</v>
       </c>
       <c r="C13">
-        <v>0.05712489001331189</v>
+        <v>0.003647954752516775</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>stage5_6</t>
+          <t>stage1_2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>log Non Verifiable Posts + Shares</t>
+          <t>log(Neutral COVID posts + shares)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Weeks 9-12</t>
+          <t>Weeks 1-4</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>neg_b_covid</t>
         </is>
       </c>
       <c r="B14">
-        <v>0.001420954209078607</v>
+        <v>-0.003415310885833308</v>
       </c>
       <c r="C14">
-        <v>0.02518239639082724</v>
+        <v>0.004730688424806732</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>stage5_6</t>
+          <t>stage1_2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>log True Posts + Shares</t>
+          <t>log(Negative COVID posts + shares)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Weeks 9-12</t>
+          <t>Weeks 1-4</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>fake</t>
+          <t>n_posts_vax</t>
         </is>
       </c>
       <c r="B15">
-        <v>-0.0384944899685522</v>
+        <v>0.0003643073351985005</v>
       </c>
       <c r="C15">
-        <v>0.0274563548904128</v>
+        <v>0.002514103145098638</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>stage5_6</t>
+          <t>stage1_2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>log Fake Posts + Shares</t>
+          <t>log(Vaccine posts + shares)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Weeks 9-12</t>
+          <t>Weeks 1-4</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>pos_b_vax</t>
+        </is>
+      </c>
+      <c r="B16">
+        <v>0.0003240114780812933</v>
+      </c>
+      <c r="C16">
+        <v>0.001749868230778863</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>stage1_2</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>log(Positive vaccine posts + shares)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Weeks 1-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>neutral_b_vax</t>
+        </is>
+      </c>
+      <c r="B17">
+        <v>1.874587871988768e-05</v>
+      </c>
+      <c r="C17">
+        <v>0.00293858050756571</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>stage1_2</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>log(Neutral vaccine posts + shares)</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Weeks 1-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>neg_b_vax</t>
+        </is>
+      </c>
+      <c r="B18">
+        <v>-0.0004941689013756917</v>
+      </c>
+      <c r="C18">
+        <v>0.001250833928195378</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>stage1_2</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>log(Negative vaccine posts + shares)</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Weeks 1-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>total_reactions</t>
+        </is>
+      </c>
+      <c r="B19">
+        <v>-0.3034388587335509</v>
+      </c>
+      <c r="C19">
+        <v>0.1447951869887975</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>stage3_4</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>log(Total reactions)</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Weeks 5-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>total_comments</t>
+        </is>
+      </c>
+      <c r="B20">
+        <v>-0.03708803338103896</v>
+      </c>
+      <c r="C20">
+        <v>0.05578999647169151</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>stage3_4</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>log(Total comments)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Weeks 5-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>total_shares</t>
+        </is>
+      </c>
+      <c r="B21">
+        <v>-0.317818047244201</v>
+      </c>
+      <c r="C21">
+        <v>0.1541366802241012</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>stage3_4</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>log(Total shares)</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Weeks 5-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>n_posts</t>
         </is>
       </c>
-      <c r="B16">
-        <v>-0.1161752773383962</v>
-      </c>
-      <c r="C16">
-        <v>0.05865570121677339</v>
-      </c>
-      <c r="D16" t="inlineStr">
+      <c r="B22">
+        <v>-0.08470616326422419</v>
+      </c>
+      <c r="C22">
+        <v>0.0829525827064579</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>stage3_4</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>log(Number of posts + shares)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Weeks 5-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>eng</t>
+        </is>
+      </c>
+      <c r="B23">
+        <v>-0.08855020275926742</v>
+      </c>
+      <c r="C23">
+        <v>0.07788693414145913</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>stage3_4</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>log(Number of posts + shares, English)</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Weeks 5-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>verifiability</t>
+        </is>
+      </c>
+      <c r="B24">
+        <v>-0.04583019266891342</v>
+      </c>
+      <c r="C24">
+        <v>0.04929102699678118</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>stage3_4</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>log(Verifiable posts + shares)</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Weeks 5-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>non_ver</t>
+        </is>
+      </c>
+      <c r="B25">
+        <v>-0.07953708633519103</v>
+      </c>
+      <c r="C25">
+        <v>0.07619082724085385</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>stage3_4</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>log(Non-verifiable posts + shares)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Weeks 5-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="B26">
+        <v>-0.01573431887632136</v>
+      </c>
+      <c r="C26">
+        <v>0.02879623134985628</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>stage3_4</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>log(True posts + shares)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Weeks 5-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>fake</t>
+        </is>
+      </c>
+      <c r="B27">
+        <v>-0.03779905807473705</v>
+      </c>
+      <c r="C27">
+        <v>0.04540832942344498</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>stage3_4</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>log(Fake posts + shares)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Weeks 5-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>n_posts_covid</t>
+        </is>
+      </c>
+      <c r="B28">
+        <v>-0.005502003722574511</v>
+      </c>
+      <c r="C28">
+        <v>0.006852958426340687</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>stage3_4</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>log(COVID posts + shares)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Weeks 5-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>pos_b_covid</t>
+        </is>
+      </c>
+      <c r="B29">
+        <v>-0.00484288300450104</v>
+      </c>
+      <c r="C29">
+        <v>0.003833127129030109</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>stage3_4</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>log(Positive COVID posts + shares)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Weeks 5-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>neutral_b_covid</t>
+        </is>
+      </c>
+      <c r="B30">
+        <v>-0.005754213433895502</v>
+      </c>
+      <c r="C30">
+        <v>0.003753329280761699</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>stage3_4</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>log(Neutral COVID posts + shares)</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Weeks 5-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>neg_b_covid</t>
+        </is>
+      </c>
+      <c r="B31">
+        <v>0.001326772493630352</v>
+      </c>
+      <c r="C31">
+        <v>0.003932970135201196</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>stage3_4</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>log(Negative COVID posts + shares)</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Weeks 5-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>n_posts_vax</t>
+        </is>
+      </c>
+      <c r="B32">
+        <v>-0.00101890186390964</v>
+      </c>
+      <c r="C32">
+        <v>0.001923365548344536</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>stage3_4</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>log(Vaccine posts + shares)</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Weeks 5-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>pos_b_vax</t>
+        </is>
+      </c>
+      <c r="B33">
+        <v>-0.0002385077111833507</v>
+      </c>
+      <c r="C33">
+        <v>0.0009510106305122785</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>stage3_4</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>log(Positive vaccine posts + shares)</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Weeks 5-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>neutral_b_vax</t>
+        </is>
+      </c>
+      <c r="B34">
+        <v>-0.001343856088304306</v>
+      </c>
+      <c r="C34">
+        <v>0.0006756041705420434</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>stage3_4</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>log(Neutral vaccine posts + shares)</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Weeks 5-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>neg_b_vax</t>
+        </is>
+      </c>
+      <c r="B35">
+        <v>0.0002271289689061846</v>
+      </c>
+      <c r="C35">
+        <v>0.001299314326519606</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>stage3_4</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>log(Negative vaccine posts + shares)</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Weeks 5-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>total_reactions</t>
+        </is>
+      </c>
+      <c r="B36">
+        <v>-0.225009138782512</v>
+      </c>
+      <c r="C36">
+        <v>0.1304068655481704</v>
+      </c>
+      <c r="D36" t="inlineStr">
         <is>
           <t>stage5_6</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>log Number of Posts + Shares</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>log(Total reactions)</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Weeks 9-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>total_comments</t>
+        </is>
+      </c>
+      <c r="B37">
+        <v>-0.04208702139993097</v>
+      </c>
+      <c r="C37">
+        <v>0.04478837775387273</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>stage5_6</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>log(Total comments)</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Weeks 9-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>total_shares</t>
+        </is>
+      </c>
+      <c r="B38">
+        <v>-0.22726420434634</v>
+      </c>
+      <c r="C38">
+        <v>0.1400976472010387</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>stage5_6</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>log(Total shares)</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Weeks 9-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>n_posts</t>
+        </is>
+      </c>
+      <c r="B39">
+        <v>-0.1267696152683789</v>
+      </c>
+      <c r="C39">
+        <v>0.06853965224634512</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>stage5_6</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>log(Number of posts + shares)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Weeks 9-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>eng</t>
+        </is>
+      </c>
+      <c r="B40">
+        <v>-0.1199061476359856</v>
+      </c>
+      <c r="C40">
+        <v>0.0653810406025966</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>stage5_6</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>log(Number of posts + shares, English)</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Weeks 9-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>verifiability</t>
+        </is>
+      </c>
+      <c r="B41">
+        <v>-0.04776672215608763</v>
+      </c>
+      <c r="C41">
+        <v>0.03962876421479993</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>stage5_6</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>log(Verifiable posts + shares)</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Weeks 9-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>non_ver</t>
+        </is>
+      </c>
+      <c r="B42">
+        <v>-0.1160449473135535</v>
+      </c>
+      <c r="C42">
+        <v>0.06668403111497767</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>stage5_6</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>log(Non-verifiable posts + shares)</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Weeks 9-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="B43">
+        <v>-0.001473211165242721</v>
+      </c>
+      <c r="C43">
+        <v>0.02748125504586487</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>stage5_6</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>log(True posts + shares)</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Weeks 9-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>fake</t>
+        </is>
+      </c>
+      <c r="B44">
+        <v>-0.04724365847483775</v>
+      </c>
+      <c r="C44">
+        <v>0.03198193712699968</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>stage5_6</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>log(Fake posts + shares)</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Weeks 9-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>n_posts_covid</t>
+        </is>
+      </c>
+      <c r="B45">
+        <v>1.31483911450334e-05</v>
+      </c>
+      <c r="C45">
+        <v>0.007617781667707903</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>stage5_6</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>log(COVID posts + shares)</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Weeks 9-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>pos_b_covid</t>
+        </is>
+      </c>
+      <c r="B46">
+        <v>-0.001123751791381956</v>
+      </c>
+      <c r="C46">
+        <v>0.003334270100071811</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>stage5_6</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>log(Positive COVID posts + shares)</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Weeks 9-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>neutral_b_covid</t>
+        </is>
+      </c>
+      <c r="B47">
+        <v>0.003445245307960508</v>
+      </c>
+      <c r="C47">
+        <v>0.003835765783131476</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>stage5_6</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>log(Neutral COVID posts + shares)</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Weeks 9-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>neg_b_covid</t>
+        </is>
+      </c>
+      <c r="B48">
+        <v>-0.003701848566871938</v>
+      </c>
+      <c r="C48">
+        <v>0.004758864052017049</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>stage5_6</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>log(Negative COVID posts + shares)</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Weeks 9-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>n_posts_vax</t>
+        </is>
+      </c>
+      <c r="B49">
+        <v>0.002083922159330145</v>
+      </c>
+      <c r="C49">
+        <v>0.001785565905225001</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>stage5_6</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>log(Vaccine posts + shares)</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Weeks 9-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>pos_b_vax</t>
+        </is>
+      </c>
+      <c r="B50">
+        <v>5.803024620644162e-06</v>
+      </c>
+      <c r="C50">
+        <v>0.001005525381730924</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>stage5_6</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>log(Positive vaccine posts + shares)</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Weeks 9-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>neutral_b_vax</t>
+        </is>
+      </c>
+      <c r="B51">
+        <v>0.001428984704264712</v>
+      </c>
+      <c r="C51">
+        <v>0.0008489445432819432</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>stage5_6</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>log(Neutral vaccine posts + shares)</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Weeks 9-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>neg_b_vax</t>
+        </is>
+      </c>
+      <c r="B52">
+        <v>0.0003811005964735312</v>
+      </c>
+      <c r="C52">
+        <v>0.001156937366629383</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>stage5_6</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>log(Negative vaccine posts + shares)</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
         <is>
           <t>Weeks 9-12</t>
         </is>
